--- a/data/GreatLink/GreatLink US Income and Growth Fund (Dis)_Dividends.xlsx
+++ b/data/GreatLink/GreatLink US Income and Growth Fund (Dis)_Dividends.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="DividendHistory" sheetId="1" r:id="GemRid498170"/>
+    <sheet name="DividendHistory" sheetId="1" r:id="GemRid718037"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>XD Date</t>
   </si>
@@ -26,10 +26,13 @@
     <t>Gross Dividend</t>
   </si>
   <si>
+    <t>19/11/2025</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
     <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>0.007</t>
   </si>
   <si>
     <t>17/09/2025</t>
@@ -478,18 +481,18 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -500,7 +503,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -522,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +536,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -544,7 +547,7 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -555,7 +558,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -566,7 +569,7 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -577,7 +580,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -588,7 +591,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -599,7 +602,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -610,18 +613,18 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -632,7 +635,7 @@
         <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -643,7 +646,7 @@
         <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -654,7 +657,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -665,7 +668,7 @@
         <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -676,7 +679,7 @@
         <v>25</v>
       </c>
       <c r="C21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -687,7 +690,7 @@
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -698,7 +701,7 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -709,7 +712,7 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -720,7 +723,7 @@
         <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -731,7 +734,7 @@
         <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -742,7 +745,7 @@
         <v>31</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -753,7 +756,7 @@
         <v>32</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -764,7 +767,7 @@
         <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -786,6 +789,17 @@
         <v>35</v>
       </c>
       <c r="C31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
         <v>4</v>
       </c>
     </row>
